--- a/output/pdf_financials_xlsx/NGMD.xlsx
+++ b/output/pdf_financials_xlsx/NGMD.xlsx
@@ -3347,22 +3347,22 @@
         <v>0.07996499999999999</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0.07996499999999999</v>
+        <v>1.00873</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>3.523132</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>3.502722</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>5.916263</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>5.438325</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>4.050806</v>
       </c>
     </row>
     <row r="93">
@@ -5824,7 +5824,11 @@
           <t>Reserves 11</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>-</t>
@@ -6418,7 +6422,11 @@
           <t>Reserves 14</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E32" t="inlineStr">
         <is>
           <t>-</t>
@@ -7010,7 +7018,11 @@
           <t>Reserves 15</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E43" t="inlineStr">
         <is>
           <t>-</t>
@@ -7902,7 +7914,11 @@
           <t>Reserves 14</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr"/>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E59" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/NGMD.xlsx
+++ b/output/pdf_financials_xlsx/NGMD.xlsx
@@ -1505,19 +1505,19 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.3365</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.472336</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.266349</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>1.749699</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.13145</v>
       </c>
       <c r="G34" s="3" t="n">
         <v>0.464456</v>
@@ -1567,19 +1567,19 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.3365</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.472336</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.266349</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>1.749699</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.13145</v>
       </c>
       <c r="G36" s="3" t="n">
         <v>0.464456</v>
@@ -1945,13 +1945,13 @@
         <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>6.232522</v>
+        <v>5.966173</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>2.121726</v>
+        <v>0.372027</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.484319</v>
+        <v>0.352869</v>
       </c>
       <c r="G48" s="3" t="n">
         <v>0.635307</v>
@@ -6480,7 +6480,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -7974,7 +7974,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E60" s="5" t="n">

--- a/output/pdf_financials_xlsx/NGMD.xlsx
+++ b/output/pdf_financials_xlsx/NGMD.xlsx
@@ -2465,22 +2465,22 @@
         <v>0</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>0.820361</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
+        <v>0.878484</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0</v>
+        <v>1.442392</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0</v>
+        <v>0.971078</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>0</v>
+        <v>0.665772</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>0</v>
+        <v>0.524505</v>
       </c>
     </row>
     <row r="65">
@@ -2592,19 +2592,19 @@
         <v>0.071912</v>
       </c>
       <c r="E68" s="3" t="n">
-        <v>0</v>
+        <v>0.878484</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>0</v>
+        <v>1.442392</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>0</v>
+        <v>0.971078</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>0</v>
+        <v>0.665772</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>0</v>
+        <v>0.524505</v>
       </c>
     </row>
     <row r="69">
@@ -2809,19 +2809,19 @@
         <v>7.158335</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>1.232902</v>
+        <v>0.354418</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>1.609771</v>
+        <v>0.167379</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>1.096396</v>
+        <v>0.125318</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>0.679511</v>
+        <v>0.013739</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>0.583474</v>
+        <v>0.058969</v>
       </c>
     </row>
     <row r="76">
